--- a/public/docs/agentpm-roi.xlsx
+++ b/public/docs/agentpm-roi.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>給与＋賞与＋社会保険を時間で割った額。分からなければ3,000円のまま</t>
+          <t>給与＋賞与＋社会保険を時間で割った額</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>控えめに見て50%。報告と転記が要らなくなる分です</t>
+          <t>控えめに見た割合。報告と転記が要らなくなる分です</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AgentPM の月額（税抜）</t>
+          <t>AgentPM の月額（すべて税抜・月払い）</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
@@ -799,7 +799,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>※ 月額は2026年9月時点の税抜価格です。最新は agentpm.app/pricing をご確認ください。</t>
+          <t>※ 月額は2026年09月時点のすべて税抜・月払いです。最新は agentpm.app/pricing をご確認ください。</t>
         </is>
       </c>
     </row>
